--- a/hospitality_forms/019_hotel_meal_service_registration--hospitality_forms.xlsx
+++ b/hospitality_forms/019_hotel_meal_service_registration--hospitality_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -803,8 +803,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -832,12 +832,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'meal_preference_breakfast',_'label':_'breakfast'}</t>
+          <t>breakfast</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'meal_preference_breakfast', 'label': 'Breakfast'}</t>
+          <t>Breakfast</t>
         </is>
       </c>
     </row>
@@ -849,12 +849,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_6,_'name':_'meal_preference_lunch',_'label':_'lunch'}</t>
+          <t>lunch</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 6, 'name': 'meal_preference_lunch', 'label': 'Lunch'}</t>
+          <t>Lunch</t>
         </is>
       </c>
     </row>
@@ -866,12 +866,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_7,_'name':_'meal_preference_dinner',_'label':_'dinner'}</t>
+          <t>dinner</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 7, 'name': 'meal_preference_dinner', 'label': 'Dinner'}</t>
+          <t>Dinner</t>
         </is>
       </c>
     </row>
@@ -883,12 +883,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_11,_'name':_'service_type_english',_'label':_'english'}</t>
+          <t>english</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 11, 'name': 'service_type_english', 'label': 'English'}</t>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -900,12 +900,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_12,_'name':_'service_type_spanish',_'label':_'spanish'}</t>
+          <t>spanish</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 12, 'name': 'service_type_spanish', 'label': 'Spanish'}</t>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -917,12 +917,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_13,_'name':_'service_type_german',_'label':_'german'}</t>
+          <t>german</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 13, 'name': 'service_type_german', 'label': 'German'}</t>
+          <t>German</t>
         </is>
       </c>
     </row>
@@ -934,12 +934,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_16,_'name':_'assigned_to_chatjimmy',_'label':_'chatjimmy'}</t>
+          <t>chatjimmy</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 16, 'name': 'assigned_to_chatjimmy', 'label': 'Chatjimmy'}</t>
+          <t>Chatjimmy</t>
         </is>
       </c>
     </row>
@@ -951,12 +951,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_17,_'name':_'assigned_to_john_doe',_'label':_'john_doe'}</t>
+          <t>john_doe</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 17, 'name': 'assigned_to_john_doe', 'label': 'John Doe'}</t>
+          <t>John Doe</t>
         </is>
       </c>
     </row>
@@ -968,12 +968,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_19,_'name':_'status_in_progress',_'label':_'in_progress'}</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 19, 'name': 'status_in_progress', 'label': 'In progress'}</t>
+          <t>In progress</t>
         </is>
       </c>
     </row>
@@ -985,12 +985,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_20,_'name':_'status_completed',_'label':_'completed'}</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 20, 'name': 'status_completed', 'label': 'Completed'}</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
@@ -1002,12 +1002,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_21,_'name':_'status_pending',_'label':_'pending'}</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 21, 'name': 'status_pending', 'label': 'Pending'}</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -1019,12 +1019,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_24,_'name':_'confirmation_true',_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 24, 'name': 'confirmation_true', 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1036,12 +1036,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_25,_'name':_'confirmation_false',_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 25, 'name': 'confirmation_false', 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
